--- a/data/seed/portfolio/L-2025-4005/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-4005/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>4756000</v>
+        <v>3696000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>390646754</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000595647999001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплта за продукцию по договору №252/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8764 01.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>1652000</v>
+        <v>2494000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №42/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №268/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,31 +642,31 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>24814000</v>
+        <v>11853000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>279636468</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000855846495001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1920 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5403</t>
         </is>
       </c>
     </row>
@@ -683,21 +683,21 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>2035000</v>
+        <v>7383000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №200/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №164/26 от 03.07.2026</t>
         </is>
       </c>
     </row>
@@ -724,21 +724,21 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>25511000</v>
+        <v>10584000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №105/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №292/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>15438000</v>
+        <v>8474000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Mehnat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>272680978</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000430892349001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №453 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за продукцию по договору №222/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -804,33 +804,28 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>8392000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>28142000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>206859450</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №125/26, НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
@@ -845,33 +840,33 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>7725000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>44466000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №2/26 от 06.07.2026</t>
+          <t>Предоплата за материалы по договору №04/26</t>
         </is>
       </c>
     </row>
@@ -887,39 +882,39 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4708000</v>
+        <v>167017000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Yulduz Plastik MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>383160768</t>
+          <t>355066892</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000592529239001</t>
+          <t>20208000612103718001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №65/26</t>
+          <t>Оплата за товары согласно с/ф №8109</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -928,34 +923,39 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>28142000</v>
+        <v>21743000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Chirchiq Non XK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №497</t>
+          <t>Оплата за товары согласно с/ф №7919</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -963,40 +963,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>200529000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>7652000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>383160768</t>
+          <t>218837940</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000592529239001</t>
+          <t>20208000621553944001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №152/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №21/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1006,21 +1006,21 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>3229000</v>
+        <v>4747000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,14 +1030,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3943 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6330</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1047,21 +1047,21 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>2315000</v>
+        <v>24577000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,14 +1071,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3098 за поставленный товар</t>
+          <t>Оплата по с/ф №219 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1086,40 +1086,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>7086000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>3326000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Ishonch Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>391164208</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000110090871001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №97/26 от 08.07.2026</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,40 +1127,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>2888000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>10526000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4126 ОТ 08.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №67/26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>3326000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>10227000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>338533115</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000790385291001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №61/22</t>
+          <t>Mahsulot uchun to'lov, shartnoma №201/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1211,38 +1211,38 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>28509000</v>
+        <v>10492000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>396985661</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000231372609001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №200/26 от 09.07.2026</t>
+          <t>Оплата по счет-фактуре №5571 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1252,38 +1252,38 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>5711000</v>
+        <v>49104000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7039 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №242/26 от 14.07.2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1291,40 +1291,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>10532000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>15051000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №262/26, НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №3200</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>20728000</v>
+        <v>15684000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Ilhom Tikuv AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>344950946</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000490542585001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9416 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №3979 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>7190000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>3837000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1646 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального наога за июнь</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,40 +1414,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>5742000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>3837000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7466 за поставленный товар</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,40 +1455,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>4462000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>14169000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №25/26 от 13.07.2026</t>
+          <t>Оплата за транспортные услуги по дог. №177/26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1496,40 +1496,35 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>2111000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>27800000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zafar Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>395449509</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4005)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000614905425001</t>
+          <t>16307000243646598417</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №143/26 от 13.07.2026</t>
+          <t>Kredit shartnomasi L-2025-4005 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1539,38 +1534,38 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>5685000</v>
+        <v>58029000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Bekobod Meva Eksport XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>234425133</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000257113115001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №124/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №2611 Т 16.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>3837000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>3679000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Оплата по счет-фактуре №4574 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1620,39 +1615,39 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3837000</v>
+        <v>10812000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №294/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1660,23 +1655,23 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>34171000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>14558000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>386164776</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000147373392001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1686,14 +1681,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5607</t>
+          <t>Оплата за товр по счет-фактуре №9839 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,35 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>27800000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>4465000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4005)</t>
+          <t>Ilhom Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16307000243646598417</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4005 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №145/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1739,38 +1739,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>120220000</v>
+        <v>12464000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Samarqand Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>396173874</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000367522895001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №226/26 от 16.07.2026</t>
+          <t>Предоплата за товар по договору №242/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1780,31 +1780,31 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>5013000</v>
+        <v>9320000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zafar Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>372585421</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000368765860001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №204/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2208 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1821,31 +1821,31 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>35546000</v>
+        <v>6073000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Andijon Poligraf XK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>363646878</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000584649556001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №191/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1246 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1862,31 +1862,31 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>12244000</v>
+        <v>3139000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Shodlik Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>390646754</t>
+          <t>264675465</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000595647999001</t>
+          <t>20208000564799938001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №9002 ОТ 20.07.2026, В .Ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1901,40 +1901,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>2586000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>14306000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SHARTNOMA №158/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товары согласно счет-фактуре №4322</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>2043000</v>
+        <v>10038000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №147/26 от 20.07.2026</t>
+          <t>Оплата по счет-фактуре №8365 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1984,39 +1984,39 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>10714000</v>
+        <v>5605000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №134/26</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2025,39 +2025,39 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>16276000</v>
+        <v>18819000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №655</t>
+          <t>Оплата за упаковочные материалы, с/ф №8255</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>2119000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>22516000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>390646754</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000595647999001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №79/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №291/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>5475000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>145582000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Предоплата за товар по договору №260/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>2079000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>12704000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Zafar Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>372585421</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000984343655001</t>
+          <t>20208000368765860001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за товар по договору №191/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>21008000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>2837000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4426</t>
+          <t>Оплата за товар по счет-фактуре №1228 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>1782000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>2079000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>396985661</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000231372609001</t>
+          <t>20208000019403908001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №270/26 от 24.07.2026</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2272,38 +2272,38 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>23959000</v>
+        <v>17222000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №238/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №7/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>10459000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>11727000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7491 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №3979</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>1923000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>24933000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>390646754</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000595647999001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6248</t>
+          <t>Xom ashyo uchun to'lov, shartn. №108/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,40 +2393,35 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>1848000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>206859450</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2075</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,40 +2429,40 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>1755000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>11510000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №293/26 от 27.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №232/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2475,40 +2470,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>23820000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>6267000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №60/26</t>
+          <t>Оплата по с/ф №6106 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,40 +2511,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>76538000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>3823000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за транспортные усуги по дог. №111/26</t>
+          <t>Оплата за товар по с/ф №4624 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,40 +2552,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>24560000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>26424000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9538</t>
+          <t>Tovarlar uchun to'lov h/f №1692</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2600,21 +2595,21 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>2466000</v>
+        <v>6450000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2624,14 +2619,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №48/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №49/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2639,40 +2634,35 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>4677000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>28818000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>272883885</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2907 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №3172</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,23 +2670,23 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>3928000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>12824000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2706,14 +2696,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8820 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товары согласно счет-фактуре №7964</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,21 +2713,21 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2616000</v>
+        <v>204262000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2747,14 +2737,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №96/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №1669 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2763,17 +2753,22 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>300000</v>
+        <v>82879000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Xiva Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2783,14 +2778,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №90/26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2800,21 +2795,21 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>7276000</v>
+        <v>18526000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2824,14 +2819,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2766 03.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №1551 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2839,40 +2834,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>43231000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>5379000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №68/26 от 04.08.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8274 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2880,40 +2875,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>245765000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>3406000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Ishonch Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>391164208</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000110090871001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4578 за поставленный товар</t>
+          <t>Арендная плата за август 2026 г. по договору №7/23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2921,40 +2916,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>6902000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>14042000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Toshkent Savdo MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>375879888</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000482708744001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №107/26 от 05.08.2026</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №168/26 ОТ 10.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2962,35 +2957,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>28818000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>9428000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №2274</t>
+          <t>Оплата за товар по счет-фактуре №836 от 11.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3000,21 +3000,21 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>5644000</v>
+        <v>4149000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3024,14 +3024,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7457 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №102/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3041,21 +3041,21 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>6280000</v>
+        <v>3551000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3065,14 +3065,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №262/26 от 10.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №5769 от 12.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3080,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>3406000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>47962000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>338533115</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000790385291001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №61/22</t>
+          <t>Оплата за продукцию по договору №136/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3122,39 +3122,39 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>15456000</v>
+        <v>3930000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №20/26, QQS bilan</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,40 +3162,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>6909000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>3930000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3203,33 +3203,33 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>11344000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>23637000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3692 13.08.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №6123</t>
         </is>
       </c>
     </row>
@@ -3282,21 +3282,21 @@
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>21500000</v>
+        <v>30440000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №85/26 от 17.08.2026</t>
+          <t>Оплата за продукцию по договору №216/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3323,21 +3323,21 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>18133000</v>
+        <v>11876000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №66/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №6584 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3364,21 +3364,21 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>6136000</v>
+        <v>7461000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5340 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №54/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3403,33 +3403,33 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>3930000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>5100000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Tur Servis AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>280094349</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000818278076001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>УПЛАТА СОЦИАЛЬНОГО НАЛОГА ЗА ИЮЛЬ</t>
+          <t>Предоплата за товар по дог. №204/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
@@ -3444,33 +3444,33 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>3930000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>4945000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Оплата по счет-фактуре №5983 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3486,39 +3486,39 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>10509000</v>
+        <v>93736000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №137/26</t>
+          <t>Оплата за товары согласно счет-фактуре №2178</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3527,39 +3527,39 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>16463000</v>
+        <v>36228000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2087</t>
+          <t>Оплата за упаковочные материалы, с/ф №6420</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3567,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>85529000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>5220000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>386164776</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000147373392001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №118/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6509 19.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>8323000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>10733000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>279636468</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000855846495001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9130 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №1500</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3651,21 +3651,21 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>6472000</v>
+        <v>5743000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6533 от 18.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №6125 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3692,38 +3692,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>5478000</v>
+        <v>5389000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №183/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №173/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>4272000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>19868000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Yulduz Plastik MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>355066892</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000612103718001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №269/26 от 18.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №5554</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3774,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>5721000</v>
+        <v>15071000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Andijon Poligraf XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>390646754</t>
+          <t>363646878</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000595647999001</t>
+          <t>20208000584649556001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9017 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №5294 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>21905000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>4755000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Qo'qon Agro MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>386164776</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000147373392001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №89/26</t>
+          <t>Предоплата за товар по договору №218/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3854,40 +3854,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>41010000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>2129000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000019403908001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №179/26 от 21.08.2026</t>
+          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>20719000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>5647000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №8/26, НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>18500000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>15192000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6123 21.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №7084</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,21 +3979,21 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>8731000</v>
+        <v>3948000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Oqtosh Poligraf XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>288388589</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000565600303001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shartnoma №194/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №235/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4018,40 +4018,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>5704000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>5294000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Mahsulot uchun to'lov, shartnoma №11/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>12528000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>17870000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4843</t>
+          <t>Оплата за продукцию по договору №126/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4102,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>14289000</v>
+        <v>10614000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>218837940</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000621553944001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №139/26 от 24.08.2026</t>
+          <t>Оплата за продукцию по договору №50/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,38 +4143,38 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>5949000</v>
+        <v>17220000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Andijon Poligraf XK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>363646878</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000584649556001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №3477 ОТ 24.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №63/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,23 +4182,23 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>2129000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>5302000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000984343655001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4208,14 +4208,14 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Оплата по с/ф №253 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>24600000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>4553000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Denov Polimer MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>269725854</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000133687658001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №82/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №6466 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4265,39 +4265,34 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>23195000</v>
+        <v>300000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>363188379</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №276/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4306,32 +4301,32 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>9600000</v>
+        <v>16055000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Avto Ehtiyot AJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>218368811</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000459371930001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4229</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №165/26</t>
         </is>
       </c>
     </row>
@@ -4347,34 +4342,39 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>300000</v>
+        <v>44798000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Chirchiq Non XK</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Предоплата за материалы по договору №189/26</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4382,23 +4382,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>23784000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>14968000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Zafar Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>372585421</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000368765860001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4408,14 +4408,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6703</t>
+          <t>Оплата по с/ф №815 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4424,32 +4424,32 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>109783000</v>
+        <v>14379000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6287</t>
+          <t>Предоплата за материалы по договору №224/26</t>
         </is>
       </c>
     </row>
@@ -4464,33 +4464,33 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>8887000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>12206000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7765 от 03.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №238/26 от 03.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4507,31 +4507,31 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>7759000</v>
+        <v>33684000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zafar Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>372585421</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000368765860001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №6/26 от 04.09.2026</t>
+          <t>Оплата по с/ф №7682 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -4547,32 +4547,32 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>289696000</v>
+        <v>6512000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4774</t>
+          <t>Оплата за упаковочные материалы, с/ф №2151</t>
         </is>
       </c>
     </row>
@@ -4589,21 +4589,21 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>17268000</v>
+        <v>19258000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4596 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №3304 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -4630,31 +4630,31 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>8972000</v>
+        <v>14680000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zafar Mebel MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>395449509</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000614905425001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №10/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4669,33 +4669,33 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>6981000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>3581000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Ishonch Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>391164208</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000110090871001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №77/26, НДС 12%</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №7/23</t>
         </is>
       </c>
     </row>
@@ -4710,33 +4710,33 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>5935000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>11694000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8247 за поставленный товар</t>
+          <t>Оплата за сырье по договору №215/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4752,32 +4752,32 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>3581000</v>
+        <v>25049000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>338533115</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000790385291001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №61/22</t>
+          <t>Оплата за товары согласно счет-фактуре №9917</t>
         </is>
       </c>
     </row>
@@ -4813,14 +4813,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №1709</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4830,38 +4830,38 @@
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>47542000</v>
+        <v>34561000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Ilhom Tikuv AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>344950946</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000490542585001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3275 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4871,21 +4871,21 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>85337000</v>
+        <v>16234000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4914 11.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №292/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4910,40 +4910,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>12148000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>9049000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Denov Polimer MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>269725854</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000133687658001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5318</t>
+          <t>Оплата за продукцию по дог. №258/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4951,40 +4951,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>7638000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>6946000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Yulduz Plastik MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>355066892</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000612103718001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4305 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №115/26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4992,40 +4992,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>6062000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>123062000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8002 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №52/26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5033,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>4131000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>8162000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>218837940</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000621553944001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Предоплата за товар по договору №20/26 от 10.09.2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5075,39 +5075,39 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>4131000</v>
+        <v>5916000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата за сырье по дог. №53/26 от 10.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5115,33 +5115,33 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>5098000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>14289000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №2677</t>
+          <t>Предоплата за товар по договору №10/26 от 11.09.2026</t>
         </is>
       </c>
     </row>
@@ -5156,40 +5156,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>16023000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>97826000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Avto Ehtiyot AJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>218368811</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000459371930001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №248/26</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1298 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5197,35 +5197,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>27800000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>33168000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4005)</t>
+          <t>Ilhom Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>299334566</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>16307000243646598417</t>
+          <t>20208000923522584001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4005 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за товар по счет-фактуре №1500 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5233,40 +5238,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>9272000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>17284000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Kamalak Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>383160768</t>
+          <t>216076865</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000592529239001</t>
+          <t>20208000252923958001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8830</t>
+          <t>Предоплата за товар по договору №98/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5276,38 +5281,38 @@
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>19949000</v>
+        <v>10681000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bekobod Un Mahsulotlari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>351993345</t>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000679235225001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6063 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1428</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5316,39 +5321,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>21162000</v>
+        <v>4131000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>383160768</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000592529239001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №105/26</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>5822000</v>
+        <v>4131000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
@@ -5382,14 +5387,14 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5398,39 +5403,39 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>40010000</v>
+        <v>17440000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Qo'qon Polimer MChJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>363188379</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000026215539001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4355</t>
+          <t>Предоплата за материалы по договору №223/26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5439,39 +5444,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>2238000</v>
+        <v>9617000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000984343655001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6521</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5479,40 +5484,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>11696000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>13946000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4495 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №180/26</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5520,40 +5525,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>10706000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>19792000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Sharq Logistik MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>363455552</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000561527723001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №118/26 от 28.09.2026</t>
+          <t>Tovarlar uchun to'lov h/f №7918</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5562,22 +5567,17 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>23192000</v>
+        <v>27800000</v>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>383160768</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4005)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000592529239001</t>
+          <t>16307000243646598417</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №118/26 ОТ 28.09.2026, НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-4005 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,40 +5602,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>228017000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>5953000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Chirchiq Non XK</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>396985661</t>
+          <t>333115279</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000231372609001</t>
+          <t>20208000385291898001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5003 29.09.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №181/26 от 16.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5643,40 +5643,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>6446000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>14493000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qog'oz MChJ</t>
+          <t>Toshkent Savdo MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>272883885</t>
+          <t>375879888</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000985656003001</t>
+          <t>20208000482708744001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №66/26, НДС 12%</t>
+          <t>Оплата за сырье по дог. №151/26 от 17.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5684,40 +5684,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>5958000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>22660000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Xiva Sut MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>206859450</t>
+          <t>336881144</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000085406966001</t>
+          <t>20208000937193053001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №273/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №3/26</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,54 +5725,505 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>18461000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>385945090</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000540696619001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5829</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>1430061000</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>1416761000</v>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>2238000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>20208000019403908001</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>5743000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>48583000</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>385945090</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>20208000540696619001</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Оплата за товар по сче-фактуре №8619 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>24467000</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>385945090</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>20208000540696619001</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №4341 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>6481000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Chirchiq Non XK</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>333115279</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>20208000385291898001</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №157/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>51315000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Yulduz Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>355066892</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20208000612103718001</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №9578</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>12220000</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>385945090</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>20208000540696619001</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №253/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>9852000</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Ilhom Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>299334566</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>20208000923522584001</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №199/26 от 29.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>48963000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Xiva Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>336881144</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20208000937193053001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №3284</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>41140000</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>385945090</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000540696619001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2817</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Bodomzor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>1429542000</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>1416242000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C139" s="4" t="n">
+      <c r="C150" s="4" t="n">
         <v>152800000</v>
       </c>
-      <c r="D139" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
